--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T10:20:05+00:00</t>
+    <t>2026-07-28T10:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:35:16+00:00</t>
+    <t>2026-07-29T12:05:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>© 2026 N. Kapan Tunçer and S. Tunçer. IG artifacts licensed under the MIT License. This IG references but does not redistribute SNOMED CT (© SNOMED International), LOINC (© Regenstrief Institute, Inc.) and the IDDSI framework (CC BY-SA 4.0, used unmodified); value sets enumerate concept identifiers only, so display terms are supplied at expansion time by the implementer's own terminology server. Implementers are responsible for holding the applicable third-party licences.</t>
+    <t>© 2026 N. Kapan Tunçer and S. Tunçer. IG artifacts licensed under the MIT License. This IG carries concept identifiers from SNOMED CT (© SNOMED International), LOINC (© Regenstrief Institute, Inc.) and the IDDSI framework (CC BY-SA 4.0, used unmodified); it redistributes no code system release, national extension or semantic content. Value sets enumerate identifiers, and some members additionally carry the English term as an unmodified display hint; the authoritative display is supplied at expansion time by the implementer's own terminology server. Implementers are responsible for holding the applicable third-party licences.</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11372" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11372" uniqueCount="813">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0</t>
+    <t>1.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T09:21:13+00:00</t>
+    <t>2026-08-13T14:00:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>© 2026 N. Kapan Tunçer and S. Tunçer. IG artifacts licensed under the MIT License. This IG carries concept identifiers from SNOMED CT (© SNOMED International), LOINC (© Regenstrief Institute, Inc.) and the IDDSI framework (CC BY-SA 4.0, used unmodified); it redistributes no code system release, national extension or semantic content. Value sets enumerate identifiers, and some members additionally carry the English term as an unmodified display hint; the authoritative display is supplied at expansion time by the implementer's own terminology server. Implementers are responsible for holding the applicable third-party licences.</t>
+    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0) and reproduced verbatim, with none translated, shortened or otherwise altered. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -1148,6 +1148,9 @@
     <t>Composition bundling swallowing assessment + severity + aspiration risk + IDDSI diet + precautions for a stroke care transition.</t>
   </si>
   <si>
+    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. LOINC® is a registered trademark of Regenstrief Institute, Inc.; LOINC codes are used under the LOINC License (http://loinc.org/license). SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0) and reproduced verbatim, with none translated, shortened or otherwise altered. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
+  </si>
+  <si>
     <t>Composition</t>
   </si>
   <si>
@@ -1782,6 +1785,9 @@
     <t>NutritionOrder constrained to bind IDDSI levels (extensible) — base FHIR only binds these 'example'.</t>
   </si>
   <si>
+    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0) and reproduced verbatim, with none translated, shortened or otherwise altered. The IDDSI framework is used unmodified under CC BY-SA 4.0; no IDDSI document text, table, image or testing method is reproduced. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
+  </si>
+  <si>
     <t>NutritionOrder</t>
   </si>
   <si>
@@ -2464,6 +2470,9 @@
   </si>
   <si>
     <t>VFSS/FEES result incl. PAS (Rosenbek). PAS lacks LOINC/SNOMED → temp code; proposed upstream.</t>
+  </si>
+  <si>
+    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0) and reproduced verbatim, with none translated, shortened or otherwise altered. LOINC® is a registered trademark of Regenstrief Institute, Inc.; LOINC codes are used under the LOINC License (http://loinc.org/license). Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
   </si>
   <si>
     <t>https://sefatuncer.github.io/stroke-dysphagia-fhir-ig/ValueSet/instrumental-swallow-type-vs</t>
@@ -2939,7 +2948,7 @@
         <v>24</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>25</v>
+        <v>359</v>
       </c>
     </row>
     <row r="35">
@@ -2963,7 +2972,7 @@
         <v>30</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="38">
@@ -2971,7 +2980,7 @@
         <v>32</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="39">
@@ -3003,7 +3012,7 @@
         <v>2</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="43">
@@ -3011,7 +3020,7 @@
         <v>4</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="44">
@@ -3027,7 +3036,7 @@
         <v>8</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="46">
@@ -3035,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="47">
@@ -3081,7 +3090,7 @@
         <v>21</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="53">
@@ -3095,7 +3104,7 @@
         <v>24</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>25</v>
+        <v>565</v>
       </c>
     </row>
     <row r="55">
@@ -3119,7 +3128,7 @@
         <v>30</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="58">
@@ -3127,7 +3136,7 @@
         <v>32</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="59">
@@ -3159,7 +3168,7 @@
         <v>2</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
     </row>
     <row r="63">
@@ -3167,7 +3176,7 @@
         <v>4</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="64">
@@ -3183,7 +3192,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
     </row>
     <row r="66">
@@ -3191,7 +3200,7 @@
         <v>10</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="67">
@@ -3237,7 +3246,7 @@
         <v>21</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
     </row>
     <row r="73">
@@ -3315,7 +3324,7 @@
         <v>2</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
     </row>
     <row r="83">
@@ -3323,7 +3332,7 @@
         <v>4</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="84">
@@ -3339,7 +3348,7 @@
         <v>8</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="86">
@@ -3347,7 +3356,7 @@
         <v>10</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="87">
@@ -3393,7 +3402,7 @@
         <v>21</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="93">
@@ -3407,7 +3416,7 @@
         <v>24</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>25</v>
+        <v>790</v>
       </c>
     </row>
     <row r="95">
@@ -3471,7 +3480,7 @@
         <v>2</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
     </row>
     <row r="103">
@@ -3479,7 +3488,7 @@
         <v>4</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="104">
@@ -3495,7 +3504,7 @@
         <v>8</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>806</v>
+        <v>809</v>
       </c>
     </row>
     <row r="106">
@@ -3503,7 +3512,7 @@
         <v>10</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="107">
@@ -3549,7 +3558,7 @@
         <v>21</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>808</v>
+        <v>811</v>
       </c>
     </row>
     <row r="113">
@@ -9061,10 +9070,10 @@
         <v>354</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -9090,13 +9099,13 @@
         <v>77</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P52" s="2"/>
       <c r="Q52" t="s" s="2">
@@ -9146,7 +9155,7 @@
         <v>20</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>75</v>
@@ -9158,7 +9167,7 @@
         <v>20</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="53">
@@ -9166,10 +9175,10 @@
         <v>354</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -9271,10 +9280,10 @@
         <v>354</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -9374,10 +9383,10 @@
         <v>354</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -9479,10 +9488,10 @@
         <v>354</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -9584,10 +9593,10 @@
         <v>354</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -9689,10 +9698,10 @@
         <v>354</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -9794,10 +9803,10 @@
         <v>354</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -9899,10 +9908,10 @@
         <v>354</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -10006,10 +10015,10 @@
         <v>354</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -10035,13 +10044,13 @@
         <v>139</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" t="s" s="2">
@@ -10091,7 +10100,7 @@
         <v>20</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>75</v>
@@ -10111,10 +10120,10 @@
         <v>354</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -10140,16 +10149,16 @@
         <v>103</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P62" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q62" t="s" s="2">
         <v>20</v>
@@ -10177,10 +10186,10 @@
         <v>161</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AA62" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AB62" t="s" s="2">
         <v>20</v>
@@ -10198,7 +10207,7 @@
         <v>20</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>83</v>
@@ -10218,10 +10227,10 @@
         <v>354</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -10247,16 +10256,16 @@
         <v>165</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P63" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q63" t="s" s="2">
         <v>20</v>
@@ -10266,7 +10275,7 @@
         <v>20</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>20</v>
@@ -10284,10 +10293,10 @@
         <v>107</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA63" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AB63" t="s" s="2">
         <v>20</v>
@@ -10305,7 +10314,7 @@
         <v>20</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>83</v>
@@ -10325,10 +10334,10 @@
         <v>354</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -10354,16 +10363,16 @@
         <v>165</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P64" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q64" t="s" s="2">
         <v>20</v>
@@ -10391,10 +10400,10 @@
         <v>179</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AB64" t="s" s="2">
         <v>20</v>
@@ -10412,7 +10421,7 @@
         <v>20</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>75</v>
@@ -10432,10 +10441,10 @@
         <v>354</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -10461,16 +10470,16 @@
         <v>183</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P65" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q65" t="s" s="2">
         <v>20</v>
@@ -10519,7 +10528,7 @@
         <v>20</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>75</v>
@@ -10539,10 +10548,10 @@
         <v>354</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -10568,14 +10577,14 @@
         <v>195</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q66" t="s" s="2">
         <v>20</v>
@@ -10624,7 +10633,7 @@
         <v>20</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>75</v>
@@ -10644,10 +10653,10 @@
         <v>354</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -10670,19 +10679,19 @@
         <v>84</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P67" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q67" t="s" s="2">
         <v>20</v>
@@ -10731,7 +10740,7 @@
         <v>20</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>83</v>
@@ -10751,10 +10760,10 @@
         <v>354</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -10777,17 +10786,17 @@
         <v>84</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q68" t="s" s="2">
         <v>20</v>
@@ -10836,7 +10845,7 @@
         <v>20</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>83</v>
@@ -10856,10 +10865,10 @@
         <v>354</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -10885,13 +10894,13 @@
         <v>278</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P69" s="2"/>
       <c r="Q69" t="s" s="2">
@@ -10941,7 +10950,7 @@
         <v>20</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>83</v>
@@ -10961,10 +10970,10 @@
         <v>354</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -10990,13 +10999,13 @@
         <v>103</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P70" s="2"/>
       <c r="Q70" t="s" s="2">
@@ -11025,10 +11034,10 @@
         <v>161</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA70" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AB70" t="s" s="2">
         <v>20</v>
@@ -11046,7 +11055,7 @@
         <v>20</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>75</v>
@@ -11066,10 +11075,10 @@
         <v>354</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -11095,16 +11104,16 @@
         <v>271</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P71" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q71" t="s" s="2">
         <v>20</v>
@@ -11153,7 +11162,7 @@
         <v>20</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>75</v>
@@ -11173,10 +11182,10 @@
         <v>354</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -11276,10 +11285,10 @@
         <v>354</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -11381,10 +11390,10 @@
         <v>354</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -11488,10 +11497,10 @@
         <v>354</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -11517,14 +11526,14 @@
         <v>103</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q75" t="s" s="2">
         <v>20</v>
@@ -11552,10 +11561,10 @@
         <v>161</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AB75" t="s" s="2">
         <v>20</v>
@@ -11573,7 +11582,7 @@
         <v>20</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>83</v>
@@ -11593,10 +11602,10 @@
         <v>354</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -11619,17 +11628,17 @@
         <v>20</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q76" t="s" s="2">
         <v>20</v>
@@ -11678,7 +11687,7 @@
         <v>20</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>75</v>
@@ -11698,10 +11707,10 @@
         <v>354</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -11724,17 +11733,17 @@
         <v>20</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q77" t="s" s="2">
         <v>20</v>
@@ -11783,7 +11792,7 @@
         <v>20</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>75</v>
@@ -11803,10 +11812,10 @@
         <v>354</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -11829,19 +11838,19 @@
         <v>84</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P78" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q78" t="s" s="2">
         <v>20</v>
@@ -11890,7 +11899,7 @@
         <v>20</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>75</v>
@@ -11910,10 +11919,10 @@
         <v>354</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11939,13 +11948,13 @@
         <v>271</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P79" s="2"/>
       <c r="Q79" t="s" s="2">
@@ -11995,7 +12004,7 @@
         <v>20</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>75</v>
@@ -12015,10 +12024,10 @@
         <v>354</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -12118,10 +12127,10 @@
         <v>354</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -12223,10 +12232,10 @@
         <v>354</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -12330,10 +12339,10 @@
         <v>354</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -12359,13 +12368,13 @@
         <v>103</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P83" s="2"/>
       <c r="Q83" t="s" s="2">
@@ -12394,10 +12403,10 @@
         <v>161</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AB83" t="s" s="2">
         <v>20</v>
@@ -12415,7 +12424,7 @@
         <v>20</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>83</v>
@@ -12435,10 +12444,10 @@
         <v>354</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -12461,13 +12470,13 @@
         <v>20</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
@@ -12518,7 +12527,7 @@
         <v>20</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>83</v>
@@ -12538,10 +12547,10 @@
         <v>354</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -12567,16 +12576,16 @@
         <v>271</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P85" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q85" t="s" s="2">
         <v>20</v>
@@ -12625,7 +12634,7 @@
         <v>20</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>75</v>
@@ -12645,10 +12654,10 @@
         <v>354</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -12748,10 +12757,10 @@
         <v>354</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -12853,10 +12862,10 @@
         <v>354</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -12960,10 +12969,10 @@
         <v>354</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -12989,13 +12998,13 @@
         <v>165</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P89" s="2"/>
       <c r="Q89" t="s" s="2">
@@ -13024,10 +13033,10 @@
         <v>179</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA89" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AB89" t="s" s="2">
         <v>20</v>
@@ -13045,7 +13054,7 @@
         <v>20</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>75</v>
@@ -13065,10 +13074,10 @@
         <v>354</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -13091,13 +13100,13 @@
         <v>84</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
@@ -13148,7 +13157,7 @@
         <v>20</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>75</v>
@@ -13168,10 +13177,10 @@
         <v>354</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -13197,10 +13206,10 @@
         <v>189</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
@@ -13251,7 +13260,7 @@
         <v>20</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>75</v>
@@ -13271,10 +13280,10 @@
         <v>354</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -13300,10 +13309,10 @@
         <v>271</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
@@ -13354,7 +13363,7 @@
         <v>20</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>75</v>
@@ -13366,7 +13375,7 @@
         <v>20</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="93">
@@ -13374,10 +13383,10 @@
         <v>354</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -13477,10 +13486,10 @@
         <v>354</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -13582,10 +13591,10 @@
         <v>354</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -13689,14 +13698,14 @@
         <v>354</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" t="s" s="2">
@@ -13718,16 +13727,16 @@
         <v>278</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P96" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Q96" t="s" s="2">
         <v>20</v>
@@ -13776,7 +13785,7 @@
         <v>20</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>75</v>
@@ -13796,10 +13805,10 @@
         <v>354</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -13825,16 +13834,16 @@
         <v>165</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P97" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="Q97" t="s" s="2">
         <v>20</v>
@@ -13862,10 +13871,10 @@
         <v>179</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AA97" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AB97" t="s" s="2">
         <v>20</v>
@@ -13883,7 +13892,7 @@
         <v>20</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>75</v>
@@ -13903,10 +13912,10 @@
         <v>354</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -13929,17 +13938,17 @@
         <v>20</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q98" t="s" s="2">
         <v>20</v>
@@ -13988,7 +13997,7 @@
         <v>20</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>75</v>
@@ -14008,10 +14017,10 @@
         <v>354</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -14037,13 +14046,13 @@
         <v>189</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P99" s="2"/>
       <c r="Q99" t="s" s="2">
@@ -14093,7 +14102,7 @@
         <v>20</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>75</v>
@@ -14113,10 +14122,10 @@
         <v>354</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -14142,13 +14151,13 @@
         <v>113</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P100" s="2"/>
       <c r="Q100" t="s" s="2">
@@ -14198,7 +14207,7 @@
         <v>20</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>75</v>
@@ -14207,7 +14216,7 @@
         <v>83</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>95</v>
@@ -14218,10 +14227,10 @@
         <v>354</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -14247,16 +14256,16 @@
         <v>103</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P101" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Q101" t="s" s="2">
         <v>20</v>
@@ -14284,10 +14293,10 @@
         <v>161</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA101" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AB101" t="s" s="2">
         <v>20</v>
@@ -14305,7 +14314,7 @@
         <v>20</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>75</v>
@@ -14325,10 +14334,10 @@
         <v>354</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -14354,16 +14363,16 @@
         <v>165</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P102" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Q102" t="s" s="2">
         <v>20</v>
@@ -14391,10 +14400,10 @@
         <v>107</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AA102" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AB102" t="s" s="2">
         <v>20</v>
@@ -14412,7 +14421,7 @@
         <v>20</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>75</v>
@@ -14432,10 +14441,10 @@
         <v>354</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -14458,16 +14467,16 @@
         <v>20</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P103" s="2"/>
       <c r="Q103" t="s" s="2">
@@ -14517,7 +14526,7 @@
         <v>20</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>75</v>
@@ -14526,7 +14535,7 @@
         <v>76</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>95</v>
@@ -14537,10 +14546,10 @@
         <v>354</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -14566,16 +14575,16 @@
         <v>165</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P104" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="Q104" t="s" s="2">
         <v>20</v>
@@ -14603,10 +14612,10 @@
         <v>107</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AA104" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AB104" t="s" s="2">
         <v>20</v>
@@ -14624,16 +14633,16 @@
         <v>20</v>
       </c>
       <c r="AG104" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>95</v>
@@ -14644,10 +14653,10 @@
         <v>354</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -14673,13 +14682,13 @@
         <v>77</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P105" s="2"/>
       <c r="Q105" t="s" s="2">
@@ -14729,7 +14738,7 @@
         <v>20</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>75</v>
@@ -14738,7 +14747,7 @@
         <v>76</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>95</v>
@@ -14746,17 +14755,17 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" t="s" s="2">
@@ -14778,13 +14787,13 @@
         <v>77</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="P106" s="2"/>
       <c r="Q106" t="s" s="2">
@@ -14834,7 +14843,7 @@
         <v>20</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>75</v>
@@ -14846,18 +14855,18 @@
         <v>20</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -14956,13 +14965,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -15059,13 +15068,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -15164,13 +15173,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -15269,13 +15278,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -15374,13 +15383,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -15479,13 +15488,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -15584,13 +15593,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -15691,13 +15700,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -15723,13 +15732,13 @@
         <v>139</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P115" s="2"/>
       <c r="Q115" t="s" s="2">
@@ -15779,7 +15788,7 @@
         <v>20</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>75</v>
@@ -15796,13 +15805,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -15825,16 +15834,16 @@
         <v>84</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="P116" s="2"/>
       <c r="Q116" t="s" s="2">
@@ -15884,7 +15893,7 @@
         <v>20</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>75</v>
@@ -15901,13 +15910,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -15933,13 +15942,13 @@
         <v>97</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="P117" s="2"/>
       <c r="Q117" t="s" s="2">
@@ -15989,7 +15998,7 @@
         <v>20</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>75</v>
@@ -16006,13 +16015,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -16038,10 +16047,10 @@
         <v>97</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" s="2"/>
@@ -16092,7 +16101,7 @@
         <v>20</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>75</v>
@@ -16109,13 +16118,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -16141,13 +16150,13 @@
         <v>103</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="P119" s="2"/>
       <c r="Q119" t="s" s="2">
@@ -16176,10 +16185,10 @@
         <v>161</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AA119" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AB119" t="s" s="2">
         <v>20</v>
@@ -16197,7 +16206,7 @@
         <v>20</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>83</v>
@@ -16214,17 +16223,17 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" t="s" s="2">
@@ -16246,16 +16255,16 @@
         <v>103</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="P120" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="Q120" t="s" s="2">
         <v>20</v>
@@ -16283,10 +16292,10 @@
         <v>161</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AA120" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AB120" t="s" s="2">
         <v>20</v>
@@ -16304,7 +16313,7 @@
         <v>20</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>83</v>
@@ -16321,13 +16330,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -16350,13 +16359,13 @@
         <v>84</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" s="2"/>
@@ -16407,7 +16416,7 @@
         <v>20</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>83</v>
@@ -16424,13 +16433,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -16456,10 +16465,10 @@
         <v>195</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
@@ -16510,7 +16519,7 @@
         <v>20</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>75</v>
@@ -16527,13 +16536,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -16556,13 +16565,13 @@
         <v>84</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
@@ -16613,7 +16622,7 @@
         <v>20</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>83</v>
@@ -16630,13 +16639,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -16659,13 +16668,13 @@
         <v>84</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
@@ -16716,7 +16725,7 @@
         <v>20</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>75</v>
@@ -16733,13 +16742,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -16762,16 +16771,16 @@
         <v>20</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="P125" s="2"/>
       <c r="Q125" t="s" s="2">
@@ -16821,7 +16830,7 @@
         <v>20</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>75</v>
@@ -16838,13 +16847,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -16870,13 +16879,13 @@
         <v>165</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="P126" s="2"/>
       <c r="Q126" t="s" s="2">
@@ -16905,10 +16914,10 @@
         <v>179</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AA126" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AB126" t="s" s="2">
         <v>20</v>
@@ -16926,7 +16935,7 @@
         <v>20</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>75</v>
@@ -16943,13 +16952,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -16975,13 +16984,13 @@
         <v>165</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="P127" s="2"/>
       <c r="Q127" t="s" s="2">
@@ -17010,10 +17019,10 @@
         <v>179</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AA127" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AB127" t="s" s="2">
         <v>20</v>
@@ -17031,7 +17040,7 @@
         <v>20</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>75</v>
@@ -17048,13 +17057,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -17080,10 +17089,10 @@
         <v>271</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" s="2"/>
@@ -17134,7 +17143,7 @@
         <v>20</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>75</v>
@@ -17143,21 +17152,21 @@
         <v>83</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -17254,13 +17263,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -17359,13 +17368,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -17466,13 +17475,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -17498,10 +17507,10 @@
         <v>165</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" s="2"/>
@@ -17531,10 +17540,10 @@
         <v>179</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AA132" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AB132" t="s" s="2">
         <v>20</v>
@@ -17552,7 +17561,7 @@
         <v>20</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>75</v>
@@ -17569,17 +17578,17 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" t="s" s="2">
@@ -17598,13 +17607,13 @@
         <v>20</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
@@ -17655,7 +17664,7 @@
         <v>20</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>75</v>
@@ -17672,13 +17681,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -17704,10 +17713,10 @@
         <v>271</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" s="2"/>
@@ -17758,7 +17767,7 @@
         <v>20</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>75</v>
@@ -17775,13 +17784,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -17878,13 +17887,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -17983,13 +17992,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -18090,13 +18099,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -18122,10 +18131,10 @@
         <v>165</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" s="2"/>
@@ -18155,10 +18164,10 @@
         <v>179</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AA138" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AB138" t="s" s="2">
         <v>20</v>
@@ -18176,7 +18185,7 @@
         <v>20</v>
       </c>
       <c r="AG138" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AH138" t="s" s="2">
         <v>75</v>
@@ -18193,13 +18202,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -18225,10 +18234,10 @@
         <v>291</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" s="2"/>
@@ -18279,7 +18288,7 @@
         <v>20</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>75</v>
@@ -18296,13 +18305,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -18328,10 +18337,10 @@
         <v>271</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" s="2"/>
@@ -18382,7 +18391,7 @@
         <v>20</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>75</v>
@@ -18399,13 +18408,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -18502,13 +18511,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -18607,13 +18616,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -18714,13 +18723,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -18746,13 +18755,13 @@
         <v>165</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="P144" s="2"/>
       <c r="Q144" t="s" s="2">
@@ -18782,7 +18791,7 @@
       </c>
       <c r="Z144" s="2"/>
       <c r="AA144" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AB144" t="s" s="2">
         <v>20</v>
@@ -18800,7 +18809,7 @@
         <v>20</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>75</v>
@@ -18817,13 +18826,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -18849,13 +18858,13 @@
         <v>165</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="P145" s="2"/>
       <c r="Q145" t="s" s="2">
@@ -18884,10 +18893,10 @@
         <v>179</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AA145" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AB145" t="s" s="2">
         <v>20</v>
@@ -18905,7 +18914,7 @@
         <v>20</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>75</v>
@@ -18922,13 +18931,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -18954,10 +18963,10 @@
         <v>165</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" s="2"/>
@@ -18988,7 +18997,7 @@
       </c>
       <c r="Z146" s="2"/>
       <c r="AA146" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AB146" t="s" s="2">
         <v>20</v>
@@ -19006,7 +19015,7 @@
         <v>20</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>75</v>
@@ -19023,13 +19032,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -19055,13 +19064,13 @@
         <v>278</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="P147" s="2"/>
       <c r="Q147" t="s" s="2">
@@ -19111,7 +19120,7 @@
         <v>20</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>75</v>
@@ -19128,13 +19137,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -19160,10 +19169,10 @@
         <v>271</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
@@ -19214,7 +19223,7 @@
         <v>20</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>75</v>
@@ -19223,7 +19232,7 @@
         <v>76</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>95</v>
@@ -19231,13 +19240,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -19334,13 +19343,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -19439,13 +19448,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -19546,13 +19555,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -19578,10 +19587,10 @@
         <v>165</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
@@ -19611,10 +19620,10 @@
         <v>179</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AA152" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AB152" t="s" s="2">
         <v>20</v>
@@ -19632,7 +19641,7 @@
         <v>20</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>75</v>
@@ -19649,13 +19658,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -19681,10 +19690,10 @@
         <v>278</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" s="2"/>
@@ -19735,7 +19744,7 @@
         <v>20</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>75</v>
@@ -19752,17 +19761,17 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="F154" s="2"/>
       <c r="G154" t="s" s="2">
@@ -19781,13 +19790,13 @@
         <v>20</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
@@ -19838,7 +19847,7 @@
         <v>20</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AH154" t="s" s="2">
         <v>75</v>
@@ -19855,13 +19864,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -19887,10 +19896,10 @@
         <v>291</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" s="2"/>
@@ -19941,7 +19950,7 @@
         <v>20</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>75</v>
@@ -19958,13 +19967,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -19990,13 +19999,13 @@
         <v>278</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="P156" s="2"/>
       <c r="Q156" t="s" s="2">
@@ -20046,7 +20055,7 @@
         <v>20</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>75</v>
@@ -20063,13 +20072,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -20095,10 +20104,10 @@
         <v>271</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" s="2"/>
@@ -20149,7 +20158,7 @@
         <v>20</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>75</v>
@@ -20158,7 +20167,7 @@
         <v>83</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>95</v>
@@ -20166,13 +20175,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -20269,13 +20278,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -20374,13 +20383,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -20481,13 +20490,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -20513,10 +20522,10 @@
         <v>165</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" s="2"/>
@@ -20546,10 +20555,10 @@
         <v>179</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="AA161" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="AB161" t="s" s="2">
         <v>20</v>
@@ -20567,7 +20576,7 @@
         <v>20</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>75</v>
@@ -20584,13 +20593,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -20616,10 +20625,10 @@
         <v>278</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" s="2"/>
@@ -20670,7 +20679,7 @@
         <v>20</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>75</v>
@@ -20687,13 +20696,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -20719,10 +20728,10 @@
         <v>165</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" s="2"/>
@@ -20752,10 +20761,10 @@
         <v>179</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="AA163" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="AB163" t="s" s="2">
         <v>20</v>
@@ -20773,7 +20782,7 @@
         <v>20</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>75</v>
@@ -20790,13 +20799,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -20822,10 +20831,10 @@
         <v>278</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" s="2"/>
@@ -20876,7 +20885,7 @@
         <v>20</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>75</v>
@@ -20893,13 +20902,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -20925,10 +20934,10 @@
         <v>291</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" s="2"/>
@@ -20979,7 +20988,7 @@
         <v>20</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>75</v>
@@ -20996,13 +21005,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -21028,10 +21037,10 @@
         <v>165</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
@@ -21061,10 +21070,10 @@
         <v>222</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="AA166" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="AB166" t="s" s="2">
         <v>20</v>
@@ -21082,7 +21091,7 @@
         <v>20</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>75</v>
@@ -21099,13 +21108,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -21131,13 +21140,13 @@
         <v>271</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="P167" s="2"/>
       <c r="Q167" t="s" s="2">
@@ -21187,7 +21196,7 @@
         <v>20</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>75</v>
@@ -21204,13 +21213,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -21307,13 +21316,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -21412,13 +21421,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -21519,17 +21528,17 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="F171" s="2"/>
       <c r="G171" t="s" s="2">
@@ -21548,13 +21557,13 @@
         <v>20</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" s="2"/>
@@ -21605,7 +21614,7 @@
         <v>20</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>75</v>
@@ -21622,13 +21631,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -21654,10 +21663,10 @@
         <v>291</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" s="2"/>
@@ -21708,7 +21717,7 @@
         <v>20</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="AH172" t="s" s="2">
         <v>75</v>
@@ -21725,13 +21734,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -21754,16 +21763,16 @@
         <v>20</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="P173" s="2"/>
       <c r="Q173" t="s" s="2">
@@ -21813,7 +21822,7 @@
         <v>20</v>
       </c>
       <c r="AG173" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AH173" t="s" s="2">
         <v>75</v>
@@ -21830,13 +21839,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -21862,10 +21871,10 @@
         <v>291</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" s="2"/>
@@ -21916,7 +21925,7 @@
         <v>20</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>75</v>
@@ -21933,13 +21942,13 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -21965,13 +21974,13 @@
         <v>278</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="P175" s="2"/>
       <c r="Q175" t="s" s="2">
@@ -22021,7 +22030,7 @@
         <v>20</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="AH175" t="s" s="2">
         <v>75</v>
@@ -22038,13 +22047,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
@@ -22073,10 +22082,10 @@
         <v>51</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="P176" s="2"/>
       <c r="Q176" t="s" s="2">
@@ -22126,7 +22135,7 @@
         <v>20</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="AH176" t="s" s="2">
         <v>75</v>
@@ -22143,7 +22152,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>31</v>
@@ -22248,7 +22257,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>82</v>
@@ -22353,7 +22362,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>90</v>
@@ -22456,7 +22465,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>96</v>
@@ -22561,7 +22570,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>102</v>
@@ -22666,7 +22675,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>111</v>
@@ -22771,7 +22780,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>118</v>
@@ -22876,7 +22885,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>125</v>
@@ -22981,7 +22990,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>133</v>
@@ -23088,7 +23097,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>138</v>
@@ -23193,7 +23202,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>143</v>
@@ -23298,7 +23307,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>149</v>
@@ -23403,7 +23412,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>155</v>
@@ -23510,7 +23519,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>164</v>
@@ -23617,7 +23626,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>172</v>
@@ -23687,7 +23696,7 @@
       </c>
       <c r="Z191" s="2"/>
       <c r="AA191" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="AB191" t="s" s="2">
         <v>20</v>
@@ -23722,7 +23731,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>182</v>
@@ -23829,7 +23838,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>188</v>
@@ -23934,7 +23943,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>193</v>
@@ -24041,7 +24050,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>200</v>
@@ -24148,7 +24157,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>207</v>
@@ -24253,7 +24262,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>212</v>
@@ -24358,7 +24367,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>217</v>
@@ -24465,7 +24474,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>225</v>
@@ -24572,7 +24581,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>233</v>
@@ -24679,7 +24688,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>241</v>
@@ -24786,7 +24795,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>247</v>
@@ -24891,7 +24900,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>253</v>
@@ -24998,7 +25007,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>260</v>
@@ -25103,7 +25112,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>265</v>
@@ -25208,7 +25217,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>270</v>
@@ -25315,7 +25324,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>277</v>
@@ -25418,7 +25427,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>282</v>
@@ -25523,7 +25532,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>285</v>
@@ -25630,7 +25639,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>290</v>
@@ -25733,7 +25742,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>295</v>
@@ -25836,7 +25845,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>298</v>
@@ -25943,7 +25952,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>305</v>
@@ -26050,7 +26059,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>312</v>
@@ -26155,7 +26164,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>317</v>
@@ -26258,7 +26267,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>320</v>
@@ -26363,7 +26372,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>325</v>
@@ -26468,7 +26477,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>330</v>
@@ -26575,7 +26584,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>335</v>
@@ -26678,7 +26687,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>336</v>
@@ -26783,7 +26792,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>337</v>
@@ -26890,7 +26899,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>338</v>
@@ -26997,7 +27006,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>342</v>
@@ -27104,7 +27113,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>346</v>
@@ -27211,7 +27220,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>350</v>
@@ -27318,7 +27327,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>351</v>
@@ -27425,7 +27434,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>31</v>
@@ -27530,7 +27539,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>82</v>
@@ -27635,7 +27644,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>90</v>
@@ -27738,7 +27747,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>96</v>
@@ -27843,7 +27852,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>102</v>
@@ -27948,7 +27957,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>111</v>
@@ -28053,7 +28062,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>118</v>
@@ -28158,7 +28167,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>125</v>
@@ -28263,7 +28272,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>133</v>
@@ -28370,7 +28379,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>138</v>
@@ -28475,7 +28484,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>143</v>
@@ -28580,7 +28589,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>149</v>
@@ -28685,7 +28694,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>155</v>
@@ -28792,7 +28801,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>164</v>
@@ -28899,7 +28908,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>172</v>
@@ -28969,7 +28978,7 @@
       </c>
       <c r="Z241" s="2"/>
       <c r="AA241" t="s" s="2">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="AB241" t="s" s="2">
         <v>20</v>
@@ -29004,7 +29013,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>182</v>
@@ -29111,7 +29120,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>188</v>
@@ -29216,7 +29225,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>193</v>
@@ -29323,7 +29332,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>200</v>
@@ -29430,7 +29439,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>207</v>
@@ -29535,7 +29544,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>212</v>
@@ -29640,7 +29649,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>217</v>
@@ -29747,7 +29756,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>225</v>
@@ -29854,7 +29863,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>233</v>
@@ -29961,7 +29970,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>241</v>
@@ -30068,7 +30077,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>247</v>
@@ -30173,7 +30182,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>253</v>
@@ -30280,7 +30289,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>260</v>
@@ -30385,7 +30394,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>265</v>
@@ -30490,7 +30499,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>270</v>
@@ -30597,7 +30606,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>277</v>
@@ -30700,7 +30709,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>282</v>
@@ -30805,7 +30814,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>285</v>
@@ -30912,7 +30921,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>290</v>
@@ -31015,7 +31024,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>295</v>
@@ -31118,7 +31127,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>298</v>
@@ -31225,7 +31234,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>305</v>
@@ -31332,7 +31341,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>312</v>
@@ -31437,7 +31446,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>317</v>
@@ -31540,7 +31549,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>320</v>
@@ -31645,7 +31654,7 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>325</v>
@@ -31750,7 +31759,7 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>330</v>
@@ -31828,14 +31837,14 @@
         <v>20</v>
       </c>
       <c r="AC268" t="s" s="2">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="AD268" s="2"/>
       <c r="AE268" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>330</v>
@@ -31855,7 +31864,7 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>335</v>
@@ -31958,7 +31967,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>336</v>
@@ -32063,7 +32072,7 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>337</v>
@@ -32170,7 +32179,7 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>338</v>
@@ -32277,7 +32286,7 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>342</v>
@@ -32384,7 +32393,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>346</v>
@@ -32491,7 +32500,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>350</v>
@@ -32598,7 +32607,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>351</v>
@@ -32705,16 +32714,16 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C277" t="s" s="2">
         <v>330</v>
       </c>
       <c r="D277" t="s" s="2">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="E277" t="s" s="2">
         <v>20</v>
@@ -32809,15 +32818,15 @@
         <v>20</v>
       </c>
       <c r="AK277" t="s" s="2">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C278" t="s" s="2">
         <v>335</v>
@@ -32917,10 +32926,10 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="C279" t="s" s="2">
         <v>336</v>
@@ -33022,10 +33031,10 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C280" t="s" s="2">
         <v>337</v>
@@ -33129,10 +33138,10 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C281" t="s" s="2">
         <v>338</v>
@@ -33180,7 +33189,7 @@
         <v>20</v>
       </c>
       <c r="T281" t="s" s="2">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="U281" t="s" s="2">
         <v>20</v>
@@ -33236,10 +33245,10 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C282" t="s" s="2">
         <v>342</v>
@@ -33265,7 +33274,7 @@
         <v>84</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="M282" t="s" s="2">
         <v>344</v>
@@ -33343,10 +33352,10 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C283" t="s" s="2">
         <v>346</v>
@@ -33450,10 +33459,10 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C284" t="s" s="2">
         <v>350</v>
@@ -33557,10 +33566,10 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C285" t="s" s="2">
         <v>351</v>
@@ -33664,7 +33673,7 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>31</v>
@@ -33769,7 +33778,7 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>82</v>
@@ -33874,7 +33883,7 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>90</v>
@@ -33977,7 +33986,7 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>96</v>
@@ -34082,7 +34091,7 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>102</v>
@@ -34187,7 +34196,7 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>111</v>
@@ -34292,7 +34301,7 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>118</v>
@@ -34397,7 +34406,7 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>125</v>
@@ -34502,7 +34511,7 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>133</v>
@@ -34609,7 +34618,7 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>138</v>
@@ -34714,7 +34723,7 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>143</v>
@@ -34819,7 +34828,7 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>149</v>
@@ -34924,7 +34933,7 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>155</v>
@@ -35031,7 +35040,7 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>164</v>
@@ -35138,7 +35147,7 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>172</v>
@@ -35208,7 +35217,7 @@
       </c>
       <c r="Z300" s="2"/>
       <c r="AA300" t="s" s="2">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="AB300" t="s" s="2">
         <v>20</v>
@@ -35243,7 +35252,7 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>182</v>
@@ -35350,7 +35359,7 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>188</v>
@@ -35455,7 +35464,7 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>193</v>
@@ -35562,7 +35571,7 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B304" t="s" s="2">
         <v>200</v>
@@ -35669,7 +35678,7 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B305" t="s" s="2">
         <v>207</v>
@@ -35774,7 +35783,7 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B306" t="s" s="2">
         <v>212</v>
@@ -35879,7 +35888,7 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B307" t="s" s="2">
         <v>217</v>
@@ -35986,7 +35995,7 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>225</v>
@@ -36093,7 +36102,7 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>233</v>
@@ -36200,7 +36209,7 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>241</v>
@@ -36307,7 +36316,7 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>247</v>
@@ -36412,7 +36421,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>253</v>
@@ -36519,7 +36528,7 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>260</v>
@@ -36624,7 +36633,7 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>265</v>
@@ -36729,7 +36738,7 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>270</v>
@@ -36836,7 +36845,7 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>277</v>
@@ -36939,7 +36948,7 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>282</v>
@@ -37044,7 +37053,7 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>285</v>
@@ -37151,7 +37160,7 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B319" t="s" s="2">
         <v>290</v>
@@ -37254,7 +37263,7 @@
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B320" t="s" s="2">
         <v>295</v>
@@ -37357,7 +37366,7 @@
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B321" t="s" s="2">
         <v>298</v>
@@ -37464,7 +37473,7 @@
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B322" t="s" s="2">
         <v>305</v>
@@ -37571,7 +37580,7 @@
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B323" t="s" s="2">
         <v>312</v>
@@ -37676,7 +37685,7 @@
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B324" t="s" s="2">
         <v>317</v>
@@ -37779,7 +37788,7 @@
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B325" t="s" s="2">
         <v>320</v>
@@ -37884,7 +37893,7 @@
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B326" t="s" s="2">
         <v>325</v>
@@ -37989,7 +37998,7 @@
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B327" t="s" s="2">
         <v>330</v>
@@ -38096,7 +38105,7 @@
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B328" t="s" s="2">
         <v>335</v>
@@ -38199,7 +38208,7 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B329" t="s" s="2">
         <v>336</v>
@@ -38304,7 +38313,7 @@
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B330" t="s" s="2">
         <v>337</v>
@@ -38411,7 +38420,7 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B331" t="s" s="2">
         <v>338</v>
@@ -38518,7 +38527,7 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B332" t="s" s="2">
         <v>342</v>
@@ -38625,7 +38634,7 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B333" t="s" s="2">
         <v>346</v>
@@ -38732,7 +38741,7 @@
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B334" t="s" s="2">
         <v>350</v>
@@ -38839,7 +38848,7 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B335" t="s" s="2">
         <v>351</v>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.1</t>
+    <t>1.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:00:50+00:00</t>
+    <t>2026-08-13T23:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0) and reproduced verbatim, with none translated, shortened or otherwise altered. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
+    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0, https://creativecommons.org/licenses/by-nd/4.0/) and reproduced verbatim, with none translated, shortened or otherwise altered. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -1148,7 +1148,7 @@
     <t>Composition bundling swallowing assessment + severity + aspiration risk + IDDSI diet + precautions for a stroke care transition.</t>
   </si>
   <si>
-    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. LOINC® is a registered trademark of Regenstrief Institute, Inc.; LOINC codes are used under the LOINC License (http://loinc.org/license). SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0) and reproduced verbatim, with none translated, shortened or otherwise altered. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
+    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. LOINC® is a registered trademark of Regenstrief Institute, Inc.; LOINC codes are used under the LOINC License (http://loinc.org/license). SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0, https://creativecommons.org/licenses/by-nd/4.0/) and reproduced verbatim, with none translated, shortened or otherwise altered. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
   </si>
   <si>
     <t>Composition</t>
@@ -1785,7 +1785,7 @@
     <t>NutritionOrder constrained to bind IDDSI levels (extensible) — base FHIR only binds these 'example'.</t>
   </si>
   <si>
-    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0) and reproduced verbatim, with none translated, shortened or otherwise altered. The IDDSI framework is used unmodified under CC BY-SA 4.0; no IDDSI document text, table, image or testing method is reproduced. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
+    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0, https://creativecommons.org/licenses/by-nd/4.0/) and reproduced verbatim, with none translated, shortened or otherwise altered. The IDDSI framework is used unmodified under CC BY-SA 4.0; no IDDSI document text, table, image or testing method is reproduced. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
   </si>
   <si>
     <t>NutritionOrder</t>
@@ -2472,7 +2472,7 @@
     <t>VFSS/FEES result incl. PAS (Rosenbek). PAS lacks LOINC/SNOMED → temp code; proposed upstream.</t>
   </si>
   <si>
-    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0) and reproduced verbatim, with none translated, shortened or otherwise altered. LOINC® is a registered trademark of Regenstrief Institute, Inc.; LOINC codes are used under the LOINC License (http://loinc.org/license). Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
+    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0, https://creativecommons.org/licenses/by-nd/4.0/) and reproduced verbatim, with none translated, shortened or otherwise altered. LOINC® is a registered trademark of Regenstrief Institute, Inc.; LOINC codes are used under the LOINC License (http://loinc.org/license). Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
   </si>
   <si>
     <t>https://sefatuncer.github.io/stroke-dysphagia-fhir-ig/ValueSet/instrumental-swallow-type-vs</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.2</t>
+    <t>1.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T23:31:20+00:00</t>
+    <t>2026-08-14T00:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.3</t>
+    <t>1.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T00:08:39+00:00</t>
+    <t>2026-08-14T00:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.4</t>
+    <t>1.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T00:48:45+00:00</t>
+    <t>2026-08-15T14:40:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.5</t>
+    <t>1.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-15T14:40:00+00:00</t>
+    <t>2026-08-18T10:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.3.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T10:55:39+00:00</t>
+    <t>2026-08-18T13:05:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.1</t>
+    <t>1.3.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T13:05:08+00:00</t>
+    <t>2026-08-18T14:23:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.2</t>
+    <t>1.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T14:23:53+00:00</t>
+    <t>2026-08-19T10:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
